--- a/data/trans_bre/P37-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P37-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,44</t>
+          <t>-1,35; 6,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,56</t>
+          <t>-5,03; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,33</t>
+          <t>-3,13; 6,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 14,94</t>
+          <t>4,67; 15,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 26,08</t>
+          <t>-4,29; 25,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 8,0</t>
+          <t>-13,6; 7,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 20,05</t>
+          <t>-8,57; 20,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,16; 29,14</t>
+          <t>8,04; 29,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,13</t>
+          <t>-2,48; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,15</t>
+          <t>-3,86; 0,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,76</t>
+          <t>-2,19; 1,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 31,34</t>
+          <t>2,45; 28,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 18,19</t>
+          <t>-31,89; 16,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-33,9; 1,83</t>
+          <t>-32,64; 4,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 18,36</t>
+          <t>-19,36; 18,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 167,75</t>
+          <t>9,12; 161,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 1,75</t>
+          <t>-6,16; 1,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 2,38</t>
+          <t>-6,17; 2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,38</t>
+          <t>-4,5; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 2,52</t>
+          <t>-7,38; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 19,2</t>
+          <t>-44,76; 19,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,25; 28,56</t>
+          <t>-47,16; 28,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 41,58</t>
+          <t>-34,89; 37,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 8,16</t>
+          <t>-20,41; 6,46</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,78</t>
+          <t>0,24; 3,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,54</t>
+          <t>-1,31; 2,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,56</t>
+          <t>-0,18; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 23,26</t>
+          <t>4,58; 22,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 29,0</t>
+          <t>1,86; 29,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 14,93</t>
+          <t>-6,83; 15,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 24,15</t>
+          <t>-1,11; 23,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 86,69</t>
+          <t>14,78; 86,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P37-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P37-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,24</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 6,42</t>
+          <t>-0,47; 6,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 2,38</t>
+          <t>-5,42; 2,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 6,48</t>
+          <t>-2,86; 6,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 15,59</t>
+          <t>7,91; 17,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 25,65</t>
+          <t>-1,54; 26,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 7,34</t>
+          <t>-14,87; 8,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 20,77</t>
+          <t>-8,13; 19,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 29,89</t>
+          <t>14,82; 36,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,07</t>
+          <t>-2,29; 1,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,48</t>
+          <t>-3,77; 0,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,75</t>
+          <t>-2,36; 1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 28,6</t>
+          <t>-0,29; 4,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 16,51</t>
+          <t>-29,5; 17,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 4,94</t>
+          <t>-32,19; 2,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 18,9</t>
+          <t>-20,92; 18,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 161,58</t>
+          <t>-1,1; 19,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,43</t>
+          <t>-1,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-7,29%</t>
+          <t>-5,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 1,74</t>
+          <t>-5,61; 2,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 2,49</t>
+          <t>-6,13; 2,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,26</t>
+          <t>-4,15; 3,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 2,0</t>
+          <t>-6,71; 2,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,76; 19,35</t>
+          <t>-42,92; 22,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,16; 28,31</t>
+          <t>-47,91; 24,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 37,83</t>
+          <t>-32,52; 39,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 6,46</t>
+          <t>-18,9; 9,14</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>5,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,72</t>
+          <t>0,26; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,53</t>
+          <t>-1,38; 2,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,51</t>
+          <t>-0,18; 3,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 22,19</t>
+          <t>2,89; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 29,17</t>
+          <t>1,67; 28,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 15,44</t>
+          <t>-7,4; 15,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 23,81</t>
+          <t>-1,1; 22,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,78; 86,41</t>
+          <t>8,95; 23,62</t>
         </is>
       </c>
     </row>
